--- a/artfynd/A 53410-2024 artfynd.xlsx
+++ b/artfynd/A 53410-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519971</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129519865</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129519843</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129519967</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129519823</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53410-2024 artfynd.xlsx
+++ b/artfynd/A 53410-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519971</v>
       </c>
       <c r="B2" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129519865</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129519843</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129519967</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129519823</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53410-2024 artfynd.xlsx
+++ b/artfynd/A 53410-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519971</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129519865</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129519843</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129519967</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129519823</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53410-2024 artfynd.xlsx
+++ b/artfynd/A 53410-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129519865</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129519843</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129519967</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
